--- a/Result/profitability/2031.xlsx
+++ b/Result/profitability/2031.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.96</v>
       </c>
       <c r="M2" t="n">
-        <v>0.39125</v>
+        <v>1.27875</v>
       </c>
       <c r="N2" t="n">
-        <v>10.26625</v>
+        <v>11.435</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>0.85375</v>
+        <v>1.51125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.6875</v>
+        <v>13.46875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.88625</v>
+        <v>1.645</v>
       </c>
       <c r="N4" t="n">
-        <v>13.455</v>
+        <v>14.445</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>-1.69</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8075000000000001</v>
+        <v>1.04375</v>
       </c>
       <c r="N5" t="n">
-        <v>7.545000000000002</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-2.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1325</v>
+        <v>0.68375</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.552499999999999</v>
+        <v>-3.8075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02000000000000001</v>
+        <v>0.5675</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.853749999999999</v>
+        <v>-6.57625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24875</v>
+        <v>0.8475</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.804999999999999</v>
+        <v>-3.52</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>-0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>0.11875</v>
+        <v>0.1187500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.121249999999998</v>
+        <v>-7.12125</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.88</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01624999999999997</v>
+        <v>-0.01624999999999992</v>
       </c>
       <c r="N10" t="n">
         <v>-7.1625</v>
@@ -1772,7 +1772,7 @@
         <v>0.17</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.19625</v>
+        <v>-0.1962499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>-8.91</v>
@@ -1899,7 +1899,7 @@
         <v>1.04</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0675</v>
+        <v>-0.06749999999999995</v>
       </c>
       <c r="N12" t="n">
         <v>-9.743749999999999</v>
@@ -2026,10 +2026,10 @@
         <v>0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>0.22125</v>
+        <v>0.2212500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.762499999999999</v>
+        <v>-3.7625</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4822</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4116</v>
+      </c>
+      <c r="E75" t="n">
+        <v>706</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>444</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1283</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1728</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1609</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.675000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="X75" t="n">
+        <v>21.77272727272727</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1843168957154406</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6057692307692306</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6591166477916195</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
